--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -53,14 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +146,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,10 +158,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,13 +777,13 @@
       <c r="C4" s="3" t="n">
         <v>569.8</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F4" s="9" t="n">
+      <c r="E4" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -802,22 +793,22 @@
         <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="9" t="n">
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>14.6</v>
+      <c r="M4" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
@@ -825,21 +816,21 @@
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>11.3</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="12" t="inlineStr"/>
-      <c r="W4" s="12" t="inlineStr"/>
+      <c r="V4" s="11" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -859,16 +850,16 @@
       <c r="C5" s="3" t="n">
         <v>512.7</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -880,35 +871,35 @@
       <c r="J5" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="9" t="n">
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>15.5</v>
+      <c r="M5" s="8" t="n">
+        <v>5.5</v>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U5" s="11" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="V5" s="3" t="n">
@@ -918,10 +909,10 @@
         <v>13.3</v>
       </c>
       <c r="X5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>16.8</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>32.2</v>
@@ -942,17 +933,17 @@
       <c r="C6" s="3" t="n">
         <v>504.8</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>33.9</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>23.9</v>
+      <c r="G6" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -963,26 +954,26 @@
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>6</v>
       </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q6" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1007,7 +998,7 @@
         <v>21.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1025,16 +1016,16 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>35.3</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1046,17 +1037,17 @@
       <c r="J7" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="9" t="n">
+      <c r="K7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>35</v>
@@ -1064,14 +1055,14 @@
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>14.4</v>
@@ -1086,10 +1077,10 @@
         <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>33.4</v>
@@ -1110,13 +1101,13 @@
       <c r="C8" s="3" t="n">
         <v>485.1</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>34.4</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1128,16 +1119,16 @@
       <c r="I8" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1147,10 +1138,10 @@
       <c r="P8" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1160,12 +1151,12 @@
         <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>21.7</v>
+        <v>31.7</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1191,16 +1182,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636.1</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>2656</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>169.7</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1113.4</v>
+      <c r="E9" s="9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>111.4</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
@@ -1214,53 +1205,53 @@
       <c r="J9" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>167.1</v>
-      </c>
-      <c r="M9" s="10" t="n">
+      <c r="K9" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="M9" s="8" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="Q9" s="9" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="Q9" s="8" t="n">
         <v>165</v>
       </c>
-      <c r="R9" s="10" t="n">
-        <v>171.8</v>
+      <c r="R9" s="8" t="n">
+        <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.8</v>
-      </c>
-      <c r="V9" s="10" t="n">
+        <v>224.1</v>
+      </c>
+      <c r="V9" s="9" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="10" t="n">
-        <v>169.6</v>
+      <c r="W9" s="9" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>120.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1278,20 +1269,20 @@
       <c r="C10" s="3" t="n">
         <v>531.2</v>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="D10" s="8" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="H10" s="11" t="n">
-        <v>47.8</v>
+      <c r="H10" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1300,10 +1291,10 @@
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1313,10 +1304,10 @@
       <c r="P10" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1328,17 +1319,17 @@
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="10" t="n">
-        <v>19.9</v>
+      <c r="W10" s="9" t="n">
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>38.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1106.2</v>
+        <v>106.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>21.2</v>
@@ -1359,14 +1350,14 @@
       <c r="C11" s="3" t="n">
         <v>427.9</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>30.8</v>
+      <c r="D11" s="8" t="n">
+        <v>30.3</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F11" s="13" t="n">
-        <v>83.8</v>
+      <c r="F11" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>13.3</v>
@@ -1374,23 +1365,23 @@
       <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" s="11" t="n">
-        <v>46.9</v>
+      <c r="I11" s="3" t="n">
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L11" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L11" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="8" t="n">
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>13</v>
@@ -1398,7 +1389,7 @@
       <c r="P11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1410,14 +1401,14 @@
       <c r="T11" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="U11" s="11" t="n">
+      <c r="U11" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="11" t="n">
-        <v>14</v>
+      <c r="W11" s="8" t="n">
+        <v>14.5</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
@@ -1438,14 +1429,14 @@
       <c r="C12" s="3" t="n">
         <v>206.7</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E12" s="12" t="inlineStr"/>
-      <c r="F12" s="11" t="n">
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1457,28 +1448,28 @@
       <c r="J12" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+      <c r="P12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R12" s="13" t="n">
+      <c r="R12" s="12" t="n">
         <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1487,17 +1478,17 @@
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U12" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V12" s="9" t="n">
+      <c r="U12" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="V12" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="W12" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" s="11" t="n">
-        <v>2.3</v>
+      <c r="W12" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>47</v>
@@ -1521,19 +1512,19 @@
       <c r="C13" s="3" t="n">
         <v>601.3</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="8" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <v>42.4</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1542,13 +1533,13 @@
       <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
@@ -1558,11 +1549,11 @@
       <c r="P13" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="11" t="n">
-        <v>15.8</v>
+      <c r="R13" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1570,13 +1561,13 @@
       <c r="T13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="V13" s="9" t="n">
+      <c r="U13" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1602,15 +1593,15 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>488</v>
-      </c>
-      <c r="D14" s="3" t="n">
+        <v>489</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F14" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1625,14 +1616,14 @@
       <c r="J14" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="11" t="n">
-        <v>22</v>
+      <c r="M14" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
@@ -1641,10 +1632,10 @@
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1653,23 +1644,23 @@
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U14" s="11" t="n">
-        <v>236</v>
-      </c>
-      <c r="V14" s="9" t="n">
+      <c r="U14" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="V14" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>114.4</v>
+        <v>14.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1685,18 +1676,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.9</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>31.5</v>
+        <v>552.1</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>31.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1708,41 +1699,41 @@
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M15" s="11" t="n">
+      <c r="L15" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>418</v>
+        <v>26.2</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>115.4</v>
+        <v>15.4</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="8" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1768,76 +1759,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.7</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>1291.6</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>2118.2</v>
+        <v>257.7</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>397.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>136.2</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>880.9</v>
-      </c>
-      <c r="M16" s="10" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="M16" s="8" t="n">
         <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>218.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>154.7</v>
       </c>
-      <c r="R16" s="10" t="n">
-        <v>173.6</v>
+      <c r="R16" s="9" t="n">
+        <v>73.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>188.2</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>131.3</v>
       </c>
-      <c r="W16" s="10" t="n">
-        <v>12.8</v>
+      <c r="W16" s="9" t="n">
+        <v>12.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1145.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1224.4</v>
+        <v>124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1853,25 +1844,25 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E17" s="10" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <v>18.5</v>
+      <c r="G17" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>11.2</v>
@@ -1879,14 +1870,14 @@
       <c r="K17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
@@ -1894,10 +1885,10 @@
       <c r="P17" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1909,14 +1900,14 @@
       <c r="U17" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>29.2</v>
@@ -1938,15 +1929,15 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>252.1</v>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="E18" s="9" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1959,26 +1950,26 @@
         <v>8</v>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>2.6</v>
+      <c r="L18" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>137.5</v>
+        <v>37.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="11" t="n">
-        <v>29.1</v>
+      <c r="Q18" s="8" t="n">
+        <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>15.2</v>
@@ -1987,16 +1978,16 @@
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
+        <v>15.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="13" t="n">
-        <v>84.40000000000001</v>
+      <c r="W18" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>8.4</v>
@@ -2005,7 +1996,7 @@
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2021,15 +2012,15 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
+        <v>526.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2041,28 +2032,28 @@
       <c r="I19" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J19" s="11" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K19" s="3" t="n">
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K19" s="8" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="8" t="n">
         <v>32</v>
       </c>
       <c r="R19" s="3" t="n">
@@ -2077,14 +2068,14 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>19</v>
@@ -2111,11 +2102,11 @@
       <c r="D20" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>20.3</v>
+      <c r="F20" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2129,17 +2120,17 @@
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="L20" s="11" t="n">
+      <c r="K20" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>55</v>
@@ -2147,7 +2138,7 @@
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="8" t="n">
         <v>28.3</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2162,10 +2153,10 @@
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="11" t="n">
+      <c r="W20" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2175,7 +2166,7 @@
         <v>32</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>118.2</v>
+        <v>18.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2191,22 +2182,22 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>42.2</v>
+        <v>542.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
@@ -2214,25 +2205,25 @@
       <c r="J21" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.7</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2242,15 +2233,15 @@
         <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2281,10 +2272,10 @@
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="8" t="n">
         <v>22.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2296,26 +2287,26 @@
       <c r="I22" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="K22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.9</v>
+        <v>9.6</v>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="8" t="n">
         <v>31.3</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2325,15 +2316,15 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="11" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W22" s="3" t="n">
+      <c r="V22" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="W22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2359,22 +2350,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2517.5</v>
-      </c>
-      <c r="D23" s="10" t="n">
+        <v>2547.5</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>160.3</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F23" s="10" t="n">
+      <c r="E23" s="8" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F23" s="9" t="n">
         <v>117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>22.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2382,28 +2373,28 @@
       <c r="J23" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K23" s="10" t="n">
+      <c r="K23" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="8" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="Q23" s="10" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>154.4</v>
       </c>
-      <c r="R23" s="14" t="inlineStr"/>
+      <c r="R23" s="13" t="inlineStr"/>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
@@ -2413,14 +2404,14 @@
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
-      <c r="V23" s="10" t="n">
+      <c r="V23" s="8" t="n">
         <v>130.5</v>
       </c>
-      <c r="W23" s="10" t="n">
-        <v>168.8</v>
+      <c r="W23" s="8" t="n">
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
@@ -2444,13 +2435,13 @@
       <c r="C24" s="3" t="n">
         <v>509.5</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2468,22 +2459,22 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M24" s="10" t="n">
+      <c r="L24" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M24" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>294.6</v>
+        <v>54.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="8" t="n">
         <v>30.9</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2498,20 +2489,20 @@
       <c r="U24" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V24" s="10" t="n">
+      <c r="V24" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2527,18 +2518,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F25" s="11" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2550,13 +2541,13 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2565,38 +2556,38 @@
       <c r="O25" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="P25" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>11.4</v>
+      <c r="P25" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="12" t="n">
+        <v>1.1</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="S25" s="11" t="n">
+      <c r="S25" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="U25" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="V25" s="9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V25" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>457.3</v>
+        <v>45.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2614,20 +2605,20 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>22</v>
+      <c r="F26" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.8</v>
+        <v>13.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>21.6</v>
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>7.3</v>
@@ -2635,20 +2626,20 @@
       <c r="J26" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2660,25 +2651,25 @@
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="U26" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>19.4</v>
+        <v>9.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>25</v>
@@ -2699,13 +2690,13 @@
       <c r="C27" s="3" t="n">
         <v>550.1</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2715,25 +2706,25 @@
         <v>12.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>16.3</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>9.9</v>
@@ -2741,29 +2732,29 @@
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>126.6</v>
+        <v>26.6</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>26.3</v>
@@ -2784,43 +2775,43 @@
       <c r="C28" s="3" t="n">
         <v>621</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>18.1</v>
+      <c r="G28" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.4</v>
+        <v>20.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P28" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="P28" s="3" t="n">
         <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
@@ -2830,15 +2821,15 @@
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>598.4</v>
+        <v>19.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="V28" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>27.7</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2869,17 +2860,17 @@
       <c r="C29" s="3" t="n">
         <v>624.9</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="8" t="n">
         <v>34.4</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="11" t="n">
-        <v>38.3</v>
+      <c r="F29" s="8" t="n">
+        <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.6</v>
@@ -2890,17 +2881,17 @@
       <c r="J29" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>41.3</v>
@@ -2911,22 +2902,22 @@
       <c r="Q29" s="3" t="n">
         <v>33.5</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U29" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>47.1</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W29" s="13" t="n">
+      <c r="W29" s="12" t="n">
         <v>3.3</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2936,7 +2927,7 @@
         <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2952,15 +2943,15 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
-      </c>
-      <c r="D30" s="10" t="n">
+        <v>271.9</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>161.6</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="9" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2970,19 +2961,19 @@
         <v>57</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>135.8</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="L30" s="9" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L30" s="8" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="10" t="n">
-        <v>30.6</v>
+      <c r="M30" s="8" t="n">
+        <v>50.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>4.3</v>
@@ -2991,27 +2982,27 @@
         <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="Q30" s="10" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="R30" s="10" t="n">
-        <v>20.9</v>
+        <v>51.7</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="R30" s="9" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>22.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>194.1</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="9" t="n">
         <v>66.8</v>
       </c>
       <c r="X30" s="3" t="inlineStr"/>
@@ -3035,15 +3026,15 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>336.4</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>556.4</v>
+      </c>
+      <c r="D31" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3055,33 +3046,33 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="11" t="n">
+      <c r="P31" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="9" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3089,20 +3080,20 @@
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>27.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3118,7 +3109,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>208.6</v>
+        <v>611.1</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
@@ -3126,7 +3117,7 @@
       <c r="E32" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3140,16 +3131,16 @@
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>5.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
@@ -3157,23 +3148,23 @@
       <c r="P32" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>33.6</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1141.1</v>
+        <v>1.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>484.1</v>
       </c>
-      <c r="V32" s="13" t="n">
-        <v>90.8</v>
+      <c r="V32" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>28.5</v>
@@ -3199,25 +3190,25 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>443.7</v>
+        <v>243.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E33" s="11" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F33" s="9" t="n">
+      <c r="E33" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F33" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
@@ -3225,10 +3216,10 @@
       <c r="K33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3240,10 +3231,10 @@
       <c r="P33" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="11" t="n">
+      <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3252,23 +3243,23 @@
       <c r="T33" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="U33" s="11" t="n">
-        <v>83.40000000000001</v>
+      <c r="U33" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="X33" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>113.9</v>
+        <v>13.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3292,17 +3283,17 @@
       <c r="E34" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3310,47 +3301,47 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>22.2</v>
+        <v>32.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>25.9</v>
+        <v>15</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="11" t="n">
-        <v>11.8</v>
+      <c r="X34" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>18.6</v>
@@ -3377,47 +3368,47 @@
       <c r="E35" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="11" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>47.1</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="Q35" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R35" s="13" t="n">
-        <v>58.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>22.8</v>
@@ -3432,7 +3423,7 @@
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>0.2</v>
@@ -3456,17 +3447,17 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="12" t="n">
         <v>45.4</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G36" s="11" t="n">
-        <v>4.8</v>
+      <c r="F36" s="8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
@@ -3477,26 +3468,26 @@
       <c r="J36" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K36" s="12" t="inlineStr"/>
-      <c r="L36" s="3" t="n">
+      <c r="K36" s="11" t="inlineStr"/>
+      <c r="L36" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3506,22 +3497,22 @@
         <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="V36" s="13" t="n">
-        <v>82.09999999999999</v>
+        <v>20.2</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="11" t="n">
-        <v>80.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>146.6</v>
+        <v>20.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>16.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3539,20 +3530,20 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>131.6</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>168.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
+      <c r="D37" s="9" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>110.3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>55.8</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
@@ -3560,51 +3551,51 @@
       <c r="J37" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="K37" s="10" t="n">
+      <c r="K37" s="9" t="n">
         <v>36.1</v>
       </c>
-      <c r="L37" s="10" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>153.2</v>
+      <c r="L37" s="8" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>53.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>44.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>2409.2</v>
+        <v>240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>359.5</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="R37" s="10" t="n">
-        <v>82.59999999999999</v>
+        <v>39.3</v>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="R37" s="8" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>171.6</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="10" t="n">
-        <v>1141.1</v>
-      </c>
-      <c r="W37" s="10" t="n">
-        <v>97</v>
+      <c r="V37" s="9" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="W37" s="9" t="n">
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>188.2</v>
+        <v>187.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3622,62 +3613,64 @@
       <c r="C38" s="3" t="n">
         <v>443.3</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E38" s="10" t="n">
+      <c r="D38" s="9" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="K38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="U38" s="11" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="10" t="n">
+      <c r="V38" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3703,48 +3696,48 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5914.6</v>
-      </c>
-      <c r="D39" s="3" t="n">
+        <v>514.6</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="11" t="n">
+      <c r="H39" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M39" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3754,12 +3747,12 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="U39" s="11" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="U39" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3790,19 +3783,19 @@
       <c r="C40" s="3" t="n">
         <v>617.1</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="11" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3814,22 +3807,22 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>21.7</v>
+        <v>2.2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>30</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3842,22 +3835,22 @@
         <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V40" s="13" t="n">
-        <v>26.8</v>
+        <v>34.2</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X40" s="11" t="n">
+      <c r="X40" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>318</v>
+        <v>30</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>223.6</v>
+        <v>23.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3875,20 +3868,20 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>16.3</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="H41" s="11" t="n">
-        <v>53</v>
+      <c r="H41" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>6.6</v>
@@ -3899,22 +3892,22 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="9" t="n">
-        <v>11.1</v>
+      <c r="M41" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="P41" s="11" t="n">
+      <c r="P41" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>29.8</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3926,20 +3919,20 @@
       <c r="T41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="U41" s="11" t="n">
+      <c r="U41" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="8" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.9</v>
+        <v>28.4</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>26.4</v>
@@ -3960,16 +3953,16 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="E42" s="9" t="n">
+      <c r="D42" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="G42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3984,10 +3977,10 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -3999,7 +3992,7 @@
       <c r="P42" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -4009,25 +4002,25 @@
         <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>128.7</v>
+        <v>28.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>13.6</v>
+      <c r="W42" s="12" t="n">
+        <v>12.3</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1392</v>
+        <v>52</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.2</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4043,21 +4036,21 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="D43" s="3" t="n">
+        <v>554</v>
+      </c>
+      <c r="D43" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="H43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
@@ -4067,24 +4060,24 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>21.5</v>
+        <v>31.5</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q43" s="9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="3" t="n">
@@ -4094,16 +4087,16 @@
         <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="U43" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4130,13 +4123,13 @@
       <c r="C44" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4152,52 +4145,52 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L44" s="9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L44" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="M44" s="9" t="n">
+      <c r="M44" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>1.8</v>
+        <v>18.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>644</v>
-      </c>
-      <c r="P44" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="P44" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q44" s="9" t="n">
+      <c r="Q44" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>87.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.2</v>
-      </c>
-      <c r="U44" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="11" t="n">
-        <v>227.9</v>
+      <c r="X44" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>290.8</v>
+        <v>50.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>112.4</v>
+        <v>12.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4213,68 +4206,68 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2312.2</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="E45" s="10" t="n">
+        <v>3312.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>113.8</v>
+      <c r="F45" s="9" t="n">
+        <v>13.7</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>910.8</v>
+        <v>91.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>7194.9</v>
+        <v>21.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K45" s="10" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="K45" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="L45" s="10" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="M45" s="10" t="n">
-        <v>1202.9</v>
+      <c r="L45" s="9" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>224</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>2.7</v>
+        <v>27</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>296.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2908.4</v>
-      </c>
-      <c r="Q45" s="10" t="n">
-        <v>178</v>
-      </c>
-      <c r="R45" s="14" t="inlineStr"/>
+        <v>58.4</v>
+      </c>
+      <c r="Q45" s="8" t="n">
+        <v>173</v>
+      </c>
+      <c r="R45" s="13" t="inlineStr"/>
       <c r="S45" s="3" t="n">
-        <v>182.8</v>
+        <v>23.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>136.9</v>
+        <v>136.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>182.6</v>
       </c>
-      <c r="V45" s="10" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>286.2</v>
+      <c r="V45" s="8" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>86.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>164.7</v>
+        <v>186.2</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4294,72 +4287,74 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="E46" s="9" t="n">
+      <c r="D46" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E46" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>22.3</v>
+      <c r="F46" s="9" t="n">
+        <v>2.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1.2</v>
+        <v>15.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>149.4</v>
+        <v>49.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="S46" s="11" t="n">
-        <v>39</v>
+        <v>15</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U46" s="11" t="n">
-        <v>390.8</v>
-      </c>
-      <c r="V46" s="10" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W46" s="10" t="n">
+      <c r="U46" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W46" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="X46" s="11" t="n">
-        <v>16.8</v>
+      <c r="X46" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>31.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
